--- a/Master Pre 180degree.xlsx
+++ b/Master Pre 180degree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hs_mann/Library/CloudStorage/OneDrive-BAFS/Thanakrit (Mann)/Man's Project/180 degree Smart Communication/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE86106-D04B-274C-870D-F81C61C793AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2A02D4-80CA-A24B-AC8E-B9FEE8172CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17400" xr2:uid="{C9818CA3-D24F-4C00-9724-87E2D8056604}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{C9818CA3-D24F-4C00-9724-87E2D8056604}"/>
   </bookViews>
   <sheets>
     <sheet name="Namelist" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="237">
   <si>
     <t>Peer1</t>
   </si>
@@ -282,9 +282,6 @@
   </si>
   <si>
     <t>Sitthipol Moungbun</t>
-  </si>
-  <si>
-    <t>sathaporn_m@bafs.co.th</t>
   </si>
   <si>
     <t>Siraprapa  Kanavapee</t>
@@ -1265,11 +1262,11 @@
     <row r="1" spans="1:12" s="3" customFormat="1" ht="20.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E1" s="22"/>
       <c r="F1" s="23" t="s">
@@ -1344,16 +1341,16 @@
         <v>58</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="K3" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1367,28 +1364,28 @@
         <v>12</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>99</v>
-      </c>
       <c r="H4" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="J4" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>146</v>
-      </c>
       <c r="K4" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1408,10 +1405,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>17</v>
@@ -1420,10 +1417,10 @@
         <v>18</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1484,16 +1481,16 @@
         <v>46</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="K7" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1513,16 +1510,16 @@
         <v>26</v>
       </c>
       <c r="F8" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>227</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>228</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>9</v>
@@ -1554,16 +1551,16 @@
         <v>79</v>
       </c>
       <c r="H9" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="I9" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>231</v>
-      </c>
       <c r="J9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1583,22 +1580,22 @@
         <v>34</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="I10" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="K10" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1618,19 +1615,19 @@
         <v>38</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="J11" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>65</v>
@@ -1659,10 +1656,10 @@
         <v>50</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>51</v>
@@ -1688,22 +1685,22 @@
         <v>46</v>
       </c>
       <c r="F13" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="K13" s="13" t="s">
         <v>160</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1723,10 +1720,10 @@
         <v>10</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>74</v>
@@ -1758,10 +1755,10 @@
         <v>42</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>78</v>
@@ -1793,22 +1790,22 @@
         <v>54</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="K16" s="13" t="s">
         <v>165</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1822,28 +1819,28 @@
         <v>56</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F17" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="H17" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="I17" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="I17" s="20" t="s">
-        <v>237</v>
-      </c>
       <c r="J17" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1863,22 +1860,22 @@
         <v>60</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1898,19 +1895,19 @@
         <v>63</v>
       </c>
       <c r="F19" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="J19" s="17" t="s">
         <v>176</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>177</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>8</v>
@@ -1933,22 +1930,22 @@
         <v>67</v>
       </c>
       <c r="F20" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="10" t="s">
-        <v>81</v>
+      <c r="K20" s="13" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="19.5" customHeight="1">
@@ -1968,22 +1965,22 @@
         <v>71</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="J21" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2009,16 +2006,16 @@
         <v>48</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2099,13 +2096,13 @@
         <v>80</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>43</v>
@@ -2120,10 +2117,10 @@
         <v>12</v>
       </c>
       <c r="J25" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2131,34 +2128,34 @@
         <v>24</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="E26" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="F26" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>93</v>
-      </c>
       <c r="H26" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J26" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="K26" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2166,34 +2163,34 @@
         <v>25</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="D27" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="F27" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="8" t="s">
+      <c r="J27" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J27" s="17" t="s">
+      <c r="K27" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2201,16 +2198,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>91</v>
-      </c>
       <c r="D28" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>23</v>
@@ -2222,13 +2219,13 @@
         <v>80</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J28" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K28" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2236,34 +2233,34 @@
         <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>93</v>
-      </c>
       <c r="D29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="F29" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="H29" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="I29" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="I29" s="8" t="s">
+      <c r="J29" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2271,34 +2268,34 @@
         <v>28</v>
       </c>
       <c r="B30" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="E30" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="F30" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2306,34 +2303,34 @@
         <v>29</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>99</v>
-      </c>
       <c r="D31" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="F31" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I31" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="J31" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2388,9 +2385,10 @@
     <hyperlink ref="K8" r:id="rId34" xr:uid="{1DFED940-11D8-4AAA-98C0-A1FD5BCAD2FE}"/>
     <hyperlink ref="G17" r:id="rId35" xr:uid="{47DDBAAF-D7BA-48F9-AA84-3167AC63CCAF}"/>
     <hyperlink ref="I17" r:id="rId36" xr:uid="{C59658AF-27BB-43E5-A76D-7DD14D2E322A}"/>
+    <hyperlink ref="K20" r:id="rId37" xr:uid="{70273298-AC65-6942-9B74-12AC5DE852B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId37"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId38"/>
 </worksheet>
 </file>
 
@@ -2411,7 +2409,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2423,19 +2421,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="F2" s="7">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2443,16 +2441,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" s="7">
         <v>4</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2460,16 +2458,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F4" s="7">
         <v>3</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2477,16 +2475,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="F5" s="7">
         <v>2</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2494,16 +2492,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2511,16 +2509,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2528,10 +2526,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E8" s="6"/>
     </row>
@@ -2540,10 +2538,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2551,10 +2549,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2562,10 +2560,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2573,10 +2571,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2584,10 +2582,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2595,10 +2593,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2606,10 +2604,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2617,10 +2615,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2628,10 +2626,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2639,10 +2637,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2650,10 +2648,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2661,10 +2659,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2751,7 +2749,7 @@
   <sheetData>
     <row r="1" spans="1:90" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A1" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2778,13 +2776,13 @@
     </row>
     <row r="2" spans="1:90">
       <c r="A2" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="C2" s="21" t="s">
         <v>135</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>136</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>7</v>
@@ -2902,32 +2900,32 @@
       <c r="BS2" s="21"/>
       <c r="BT2" s="21"/>
       <c r="BU2" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BV2" s="21"/>
       <c r="BW2" s="21"/>
       <c r="BX2" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BY2" s="21"/>
       <c r="BZ2" s="21"/>
       <c r="CA2" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="CB2" s="21"/>
       <c r="CC2" s="21"/>
       <c r="CD2" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="CE2" s="21"/>
       <c r="CF2" s="21"/>
       <c r="CG2" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="CH2" s="21"/>
       <c r="CI2" s="21"/>
       <c r="CJ2" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="CK2" s="21"/>
       <c r="CL2" s="21"/>
@@ -2937,265 +2935,265 @@
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
       <c r="D3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="G3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="J3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="M3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="P3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="S3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="U3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="T3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="V3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="X3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="W3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="Y3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="Z3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AB3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AC3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AE3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AF3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AH3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AI3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AK3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AL3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AN3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AP3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AO3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AP3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AQ3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AR3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AR3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AS3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AT3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AV3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AU3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AV3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AW3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AX3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AY3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="AZ3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BA3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BB3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BC3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BD3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BD3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BE3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BF3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BH3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BG3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BH3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BI3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BJ3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BK3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BJ3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BL3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BM3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BN3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BM3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BN3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BO3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BP3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BQ3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BP3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BQ3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BR3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BS3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BT3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BS3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BT3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BU3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BW3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BV3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BW3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BX3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BY3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="BZ3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BY3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="BZ3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="CA3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CB3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="CC3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="CB3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="CC3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="CD3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CE3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="CF3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="CE3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="CF3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="CG3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CH3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="CI3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="CH3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="CI3" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="CJ3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CK3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="CL3" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="CK3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="CL3" s="6" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:90">
@@ -3203,10 +3201,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:90">
@@ -3214,10 +3212,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:90">
@@ -3225,10 +3223,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:90">
@@ -3236,10 +3234,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:90">
@@ -3247,10 +3245,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:90">
@@ -3258,10 +3256,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:90">
@@ -3269,10 +3267,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:90">
@@ -3280,10 +3278,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:90">
@@ -3291,10 +3289,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:90">
@@ -3302,10 +3300,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:90">
@@ -3313,10 +3311,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:90">
@@ -3324,10 +3322,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:90">
@@ -3335,10 +3333,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3346,10 +3344,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3357,10 +3355,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3368,10 +3366,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3379,10 +3377,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3390,10 +3388,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3401,10 +3399,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Master Pre 180degree.xlsx
+++ b/Master Pre 180degree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hs_mann/Library/CloudStorage/OneDrive-BAFS/Thanakrit (Mann)/Man's Project/180 degree Smart Communication/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2A02D4-80CA-A24B-AC8E-B9FEE8172CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFA367C-9C06-5E4D-9752-383570CE7535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{C9818CA3-D24F-4C00-9724-87E2D8056604}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{C9818CA3-D24F-4C00-9724-87E2D8056604}"/>
   </bookViews>
   <sheets>
     <sheet name="Namelist" sheetId="1" r:id="rId1"/>
